--- a/www/download/IND.gross_output.s.du.WIOD16.xlsx
+++ b/www/download/IND.gross_output.s.du.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175585.415122595</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>167346.616512851</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178018.889577661</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>208325.99456084</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244137.771688634</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>272483.416958212</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>295760.34042499</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356426.966089289</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>390149.187371742</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>357345.763322821</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>410554.982346412</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>499417.161162418</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482387.840217582</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483008.512455872</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474222.337663865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72961.8494403452</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71900.1968509398</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69530.0695574608</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79554.0122072962</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89050.944239269</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92997.062725466</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102803.92790463</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117725.563352436</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131901.571232918</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116022.194255488</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133040.04095906</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155850.806968127</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151528.191128171</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157120.281891231</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149226.500781491</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91427.3907174332</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87239.8586578659</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85716.9961940978</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99783.0898809414</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118582.952765256</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124016.533276105</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142280.875972936</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169907.499357072</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190901.626602483</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160716.647049447</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198947.725475864</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247062.315929284</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221289.544538334</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218880.601091859</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237974.010596405</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55875.9171076828</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54794.901633477</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54865.2531147039</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59650.6258938543</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67514.6205383206</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71476.1848424209</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80151.5681847918</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92886.6082275299</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105225.357823272</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90058.4513377725</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88122.625350105</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94639.9403273093</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88794.6789892671</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89261.9585357351</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95769.5379072208</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1305030.74789548</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1262860.22595495</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1323370.11023873</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1492379.76582471</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1719986.87559441</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.898</t>
+          <t>1897776.62764767</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1969438.49401687</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2239757.37224778</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>2539521.37367978</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>2214271.27631345</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>2522672.79435749</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>2701256.96043228</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>2611505.06925249</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>2644431.2503365</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>2693904.97460361</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227157.426794193</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218913.548950582</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>221107.979735748</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252208.884616033</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>294024.135117266</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>318843.8114663</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345845.4875631</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382662.131348436</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>418258.291722978</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>362863.171002687</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430204.5059939</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495677.735767232</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494784.237140308</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473345.994712012</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>482881.429871818</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16.828</t>
+          <t>16827538.3632182</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16.319</t>
+          <t>16319670.6326982</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.418</t>
+          <t>16419066.7397775</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.292</t>
+          <t>18293520.2174473</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20960410.7594234</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.602</t>
+          <t>23602746.1228143</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26.832</t>
+          <t>26831736.8935333</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31.529</t>
+          <t>31529721.1311535</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36.369</t>
+          <t>36367619.5427881</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>35.153</t>
+          <t>35151736.4033352</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>38.363</t>
+          <t>38362359.0872924</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>45.261</t>
+          <t>45261550.3586182</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>45.721</t>
+          <t>45720808.2372245</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>46.337</t>
+          <t>46337531.3974834</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>45.756</t>
+          <t>45756665.2508413</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4527.55313171075</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5206.44382533463</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5903.60900955616</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6746.04929216796</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6711.47530961475</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7057.11035477559</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6891.13467164354</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8263.13952264611</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10763.4039610074</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8566.50246919754</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8640.05640405001</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8957.20134702745</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7883.74186928583</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7501.90676394573</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7376.2731861304</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91472.2623257613</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88660.8124424059</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90913.331488038</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99922.9664740661</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112414.290100837</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123007.627942416</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134719.667379593</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157266.129488859</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174715.167128248</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>144021.357084318</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165129.073046567</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190662.815083237</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174261.392387179</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177701.407917291</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179209.981656313</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>634816.386027917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>604372.369733503</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>587641.585717621</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>677274.542654608</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>767865.416931396</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>824210.857566878</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>923126.81899935</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1066789.52969047</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1166306.1616023</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>956467.630590464</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1092919.08593587</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1269042.11046461</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1172085.39300915</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1182825.42695012</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1169339.26705234</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53388.434953538</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53846.1985891745</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54612.0981228939</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65189.451696275</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74102.3868837519</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80979.7764488889</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80555.5797311417</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94976.9654460105</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109716.617898298</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87626.9251455449</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89159.0296624006</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98994.3460335095</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94862.6219083646</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99984.2386974088</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97140.9450089368</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>311319.699758727</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>313304.715096243</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335979.508183834</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377412.252120832</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437343.036265442</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>489768.800264381</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>547921.038331832</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630902.192909868</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>681201.786210204</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>515564.312772881</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>610244.491657643</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>688006.260511743</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>635540.631770362</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>612458.800970001</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>623344.85161777</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10469.3224972221</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10377.2311136395</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11335.9373220649</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13280.0278381185</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14434.6295910244</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15553.7157755108</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18468.3060709894</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20408.9065753439</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21852.5090801504</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15400.5234101671</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16879.3159249937</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21850.9386347268</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20527.6053049307</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20093.6442118897</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20942.8226008739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55041.7962492808</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53008.654163666</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53704.0658855076</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62958.1561040825</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71819.1749149873</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79472.244924884</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87082.1477653738</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99175.8416590771</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116249.48034054</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79506.9309663126</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87166.1439166624</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97291.7351180329</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92813.3799667543</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89480.6266765698</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86566.1248732729</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377619.503363528</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>367459.185064231</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362356.700926086</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>412604.91369696</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>487282.135881158</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>525161.135479389</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>566037.174845553</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>652903.507556169</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>721068.649713558</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>621526.252211998</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>672378.611910563</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>792437.849108004</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>722538.055681103</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>692893.077507582</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>687523.208602251</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>377368.596296163</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>371637.31342468</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>375549.88808132</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>416383.84732609</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>468917.44700712</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>513750.935888169</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>549209.436060697</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606457.581592018</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>630839.165196732</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>577062.508092607</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>647821.42948431</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>731253.709805111</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>733705.718594573</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>758257.608969588</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>719225.68303137</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67594.4882074091</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65608.3648199722</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64164.9241404664</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71801.029082782</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76954.0930010286</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89701.8522515634</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97700.5269186955</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113540.423220784</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118895.640490919</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104415.262259344</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104996.44420376</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108283.464217097</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94004.0928700795</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96305.9616278859</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101720.927120836</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88171.074075256</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86311.4776296078</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87511.6462055534</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93668.699031557</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101931.407740804</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108580.841477803</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116032.725612693</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128206.831252899</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>135562.526649701</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114914.453083988</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118844.261690612</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129241.232189508</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116098.408825391</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>115405.014722637</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126174.346487731</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1317265.31560639</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1368491.62499289</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.481</t>
+          <t>1481130.36124513</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1768438.37390889</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>1944444.69874403</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1869810.14025494</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>1953716.96002463</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.286</t>
+          <t>2286266.74609433</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.542</t>
+          <t>2541925.91180378</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.424</t>
+          <t>2423684.16507267</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.731</t>
+          <t>2731311.59681978</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.916</t>
+          <t>2916429.98037989</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.083</t>
+          <t>3083628.54968509</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3360123.26992706</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3.727</t>
+          <t>3726734.4342725</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.148</t>
+          <t>10148501.7601139</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.295</t>
+          <t>10296174.031567</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.685</t>
+          <t>10686076.7934919</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12.303</t>
+          <t>12304336.007754</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>13981250.6092664</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14.856</t>
+          <t>14856680.0264169</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15.593</t>
+          <t>15592073.6564729</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.631</t>
+          <t>17632161.8948117</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>18961167.4328455</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17439390.7369658</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>19.511</t>
+          <t>19511971.1302925</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>21.017</t>
+          <t>21018738.9343211</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>22.816</t>
+          <t>22817736.1589876</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>24980309.9544013</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>26.839</t>
+          <t>26839027.0524405</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32701.8906474058</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37008.7679568021</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37105.5387058364</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44722.4476939921</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51527.940353664</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60873.9520267049</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70154.2427845465</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75444.1059949567</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75715.9602586461</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64153.5584358355</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52392.0702088935</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65063.9667462982</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61396.4551033331</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67903.8033237925</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67893.3758207943</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>466242.291514899</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459169.636178279</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459047.103328985</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>515211.428718561</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>595415.300067081</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>635859.009815687</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>717484.419754137</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806713.877676542</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>882933.018575956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>697164.443595809</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>830291.866542988</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955792.170768514</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>836315.566710241</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>802527.362675785</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>799327.179244097</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1620994.54334283</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1524256.46300703</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>1472973.34689901</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1660783.85637604</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.911</t>
+          <t>1908059.53050491</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.043</t>
+          <t>2040056.75235416</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>2201058.66667794</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2409422.97539756</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>2704071.81762024</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.186</t>
+          <t>2189002.69853509</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.515</t>
+          <t>2514906.11991461</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2.966</t>
+          <t>2961438.57960092</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.869</t>
+          <t>2864508.85306208</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.696</t>
+          <t>2694033.18635129</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>2662798.66473898</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>603595.936884305</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>578919.957873999</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601464.706816159</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>683077.520072836</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>819514.920569617</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>874777.065684101</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>993069.315743809</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1081633.99441348</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>1230809.28520793</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1076831.04722049</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1238843.06351221</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>1535394.99144993</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1495056.54651192</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1538537.54250057</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1.567</t>
+          <t>1567461.365664</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26327.5057491029</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25143.332921318</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25614.5142239903</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28781.2489862928</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29804.4631032039</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32881.0285493816</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34883.4263221099</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37887.8206702807</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42844.6639294685</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32220.6890686986</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33534.5050080409</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37872.2671861567</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37180.9425186627</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36971.211160822</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42280.6083139634</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3482.90227780211</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3609.25723962152</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3566.46636005606</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4210.19687876538</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5056.76557503083</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5455.73086480707</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6180.23693274446</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7269.87277549434</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8925.98567698761</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7836.6529667163</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9642.41248914173</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.5984696416</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9660.48754052097</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8782.67536874226</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9089.11958904991</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17467.2720062716</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17702.5746530721</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17711.2002812163</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20244.0119708307</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21548.9086011814</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23386.2166377377</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27254.3609710815</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30516.718240154</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32968.7954905556</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23078.5653804689</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23312.5356471972</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27307.939326381</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27896.7654233693</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27322.8898089266</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28319.2997971392</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>618025.875840788</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>603405.345249499</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604316.199634441</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>661151.747284779</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>759739.552743118</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>815486.565654301</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>901159.134259637</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1029576.9278164</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1117491.39030759</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>969443.540193991</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.106</t>
+          <t>1106009.57602913</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.192</t>
+          <t>1191702.5382499</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1189841.21798007</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>1188304.67991198</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1199793.18511129</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2798.17145122976</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2519.08332709182</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2406.63883179843</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2859.12574137855</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2949.22980168095</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3163.61789530174</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3401.72225538562</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4063.13870575219</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5251.99779137294</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4320.64489205989</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4955.92788839706</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4779.03101474672</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4865.3702501026</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4708.52706842002</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4319.91833130665</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>154712.519881416</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160851.700009294</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168189.611354549</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222454.000251186</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233736.737008926</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245215.781761123</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262759.644006053</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>306762.083946797</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362216.076482773</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>355234.149117037</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>406825.394919421</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>459949.342291283</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>421426.302590783</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>478820.851454815</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482306.469140745</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>274226.435662529</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278439.645564394</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256250.637668869</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279041.276161324</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>315865.204561903</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346874.247373849</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>378821.699050054</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>446736.414423073</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>510124.023793971</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>449267.581788946</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>511621.598539622</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568230.116540166</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>536002.027254542</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>535934.226019191</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>541945.546722055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113966.453029901</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111318.772243646</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109435.318609537</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118114.854243043</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134759.993166213</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136757.655566375</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145024.853132887</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164815.948869764</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181707.799762009</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142239.773433676</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155677.579585959</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174368.804453051</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157440.775569306</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158233.311597584</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161816.735687223</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273292.368853789</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263876.859230536</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221664.930264897</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>245897.105677109</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257238.026891644</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273446.390547135</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278903.082468789</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322263.420056239</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>342475.315007184</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>302287.1140086</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316122.863966993</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>340719.80660482</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256019.240977592</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254941.051650042</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>257846.534212679</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1286981.43118862</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.275</t>
+          <t>1275467.92458565</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>1262049.21732588</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.392</t>
+          <t>1392327.52779567</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1479720.22636252</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1621983.80288407</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.702</t>
+          <t>1701534.68117358</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.923</t>
+          <t>1923131.65539531</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>1962813.48494936</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.712</t>
+          <t>1711834.76156452</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1916593.73970827</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2.031</t>
+          <t>2031140.93270274</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.029</t>
+          <t>2029399.6560179</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1.949</t>
+          <t>1949257.18439902</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>1829012.99024575</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37443.2763667251</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37056.1385598626</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36832.4002275355</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40834.7157054659</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45894.5966362946</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50337.1032393548</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58288.6063612809</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69644.3514997283</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77297.32720357</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69746.7619741055</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73035.0001285121</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85777.614346037</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81272.1972870936</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82537.0051052019</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84289.0359169522</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16783.2498433523</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16610.8033661159</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16741.7478153549</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18750.5880910525</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22629.3103913685</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23800.774231195</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25686.019719939</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29398.8914535006</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32452.9442600741</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26759.5758590886</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29525.9046193998</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32600.7176751218</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29480.5762612495</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28514.0854423724</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29101.640716982</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79056.717789855</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74007.1025755639</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73169.8048012069</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82448.9887250478</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97151.0344255723</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105899.092140872</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112797.891646188</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127909.971692112</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141337.664375276</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114467.83813937</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130712.352695056</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149727.43435635</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140054.903726976</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140137.137183001</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139090.736163906</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>543229.229075593</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>511974.091352868</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>484956.629178399</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>535437.639905317</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>620239.244103346</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>664658.348746005</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>690905.276783067</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769261.701277648</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>835549.961078271</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>719010.90689849</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>875856.312772392</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>999138.91814117</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>993033.502390589</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1056636.22584802</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1159751.11683886</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>408727.810687665</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>366319.90980768</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389414.676420874</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>450762.796459691</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>549043.320946067</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588104.553016171</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>643665.897086475</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718106.982154989</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>774829.627018902</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>619773.903369224</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>774519.178151199</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>870711.710322065</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>834089.602473707</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>836254.802044916</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>875006.420149148</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>2273291.2782731</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>2115932.32794027</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2115209.41183676</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2319323.60188529</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.675</t>
+          <t>2674593.26278721</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>3004615.37180223</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.237</t>
+          <t>3236469.56182719</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.483</t>
+          <t>3481241.51754435</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3.739</t>
+          <t>3738608.14612839</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.861</t>
+          <t>2860071.28061384</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3248324.22885455</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>3762297.81504212</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>3.695</t>
+          <t>3694844.97274404</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>3.626</t>
+          <t>3625387.59136901</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>3.748</t>
+          <t>3748675.83765389</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20.928</t>
+          <t>20928754.2959547</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>21.124</t>
+          <t>21126311.9652425</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>22.628</t>
+          <t>22630797.9416875</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25.629</t>
+          <t>25630547.7495081</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>29231282.3971624</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>32.945</t>
+          <t>32945658.7860837</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>36.388</t>
+          <t>36387112.7618615</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.238</t>
+          <t>41242148.8545518</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>46.058</t>
+          <t>46060957.8720781</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>43.155</t>
+          <t>43154599.170116</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>47741479.4565505</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>53.175</t>
+          <t>53180164.7411287</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>55.608</t>
+          <t>55611543.7946977</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>58.175</t>
+          <t>58175268.9562369</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>60.735</t>
+          <t>60736549.2796353</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>62.23</t>
+          <t>62229753.3193865</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>61.605</t>
+          <t>61604960.2125258</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>63.686</t>
+          <t>63685981.2160894</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>71.977</t>
+          <t>71977032.6483746</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>82.077</t>
+          <t>82076833.9959776</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>90.664</t>
+          <t>90663628.2520401</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>99.536</t>
+          <t>99535949.1494321</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>113.719</t>
+          <t>113719038.465387</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>126.935</t>
+          <t>126934817.736997</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>117.37</t>
+          <t>117369540.767418</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>130.256</t>
+          <t>130255885.319046</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>147.275</t>
+          <t>147274986.659704</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>151.14</t>
+          <t>151139918.668272</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>156.583</t>
+          <t>156582791.006788</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>160.997</t>
+          <t>160997197.961565</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24267.752594956</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23564.3128127579</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24584.204055909</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26690.512800098</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31223.4553673213</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32655.7273702739</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35288.1756503391</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40315.9942082245</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45876.3891647709</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39040.8534372518</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41630.9839515365</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43768.2423755102</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40321.9294892239</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39535.353162466</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39364.020024182</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89810.7908311525</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85867.7484401749</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85211.7327624005</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94938.1553768188</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102436.632762003</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114159.166271738</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>125631.802690146</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139681.686381608</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157689.865155065</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137056.849485447</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147222.719636721</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180337.470443646</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174783.021377537</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176860.50470307</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178940.992605747</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40440.0167357196</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38442.0886666181</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38710.7489824389</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42982.6446543517</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48225.0810811757</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53446.6867468365</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56860.9097875489</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68682.5986447112</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76026.9215382379</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62936.9405815446</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69487.4950005652</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80055.0540498697</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76700.4109629904</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78459.906552239</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77247.9290248958</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
